--- a/demos/PrintSharp.WinForms.Demo/Templates/Grid.xlsx
+++ b/demos/PrintSharp.WinForms.Demo/Templates/Grid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Src\Git\PrintSharp\demos\PrintSharp.WinForms.Demo\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B884EBD3-C966-45B9-ADE2-84153F8B9359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46859201-0301-42E5-ACC9-FDA05A4EEE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -112,19 +112,26 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Meiryo"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,6 +152,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,11 +226,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -236,13 +246,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,101 +579,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -665,7 +681,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
   </mergeCells>
-  <phoneticPr fontId="5"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
